--- a/initial_fa_data/fa_classification_criterion.xlsx
+++ b/initial_fa_data/fa_classification_criterion.xlsx
@@ -296,7 +296,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="48.49"/>
